--- a/docs/Robot_BOM.xlsx
+++ b/docs/Robot_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bryan Heddle\OneDrive\Desktop\Ergos-Dynamic-Humanoid-Platform\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CF7321-4CC5-4A11-9E0E-015C31A4BDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD83E80-55EC-45C4-B5FD-981DB355D76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{02CBD0F1-74CF-4889-91DA-ED3C1ACE063A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Part</t>
   </si>
@@ -164,12 +164,6 @@
     <t>3D printing material used for lightweight housings and custom mounts throughout the robot prototype to allow iterative design, it's likely I'll need lots of PLA due to continous prints, and like mentioned, fixes.</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/short/0zvnp1rd</t>
-  </si>
-  <si>
-    <t>JLCPCB [view quote image]</t>
-  </si>
-  <si>
     <t>OAK-D Lite</t>
   </si>
   <si>
@@ -201,6 +195,15 @@
   </si>
   <si>
     <t>Patriot P320 128GB SSD</t>
+  </si>
+  <si>
+    <t>14 AWG Red and Black Wire</t>
+  </si>
+  <si>
+    <t>JLCPCB</t>
+  </si>
+  <si>
+    <t>Digikey</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="8">
         <f>SUM(F3:F36)</f>
-        <v>2960.0236999999997</v>
+        <v>2876.4036999999998</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="60.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -765,10 +768,10 @@
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>30</v>
@@ -807,10 +810,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>31</v>
@@ -934,7 +937,7 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>35</v>
@@ -955,7 +958,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>39</v>
@@ -964,14 +967,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="F17" s="4">
         <f>(D17*E17)*1.13</f>
-        <v>206.79</v>
+        <v>123.16999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="F18">
         <f t="shared" si="1"/>
@@ -1014,13 +1020,13 @@
     </row>
     <row r="22" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1035,10 +1041,10 @@
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>37</v>
@@ -1067,7 +1073,7 @@
     <hyperlink ref="B15" r:id="rId7" display="https://www.amazon.ca/DXF-Battery-Hardcase-Airplane-Helicopter/dp/B09TDFVWHS/ref=sr_1_1?dib=eyJ2IjoiMSJ9.riuler2SJ2K370oVwQohtNzuSRoCNMr3AgKZDJKD89us8ngrWmuQdQl3ogluOg-ASMoJJ5PtQqXOHwWlzm9_BE894ZhAyBr1AwkwDSZmq8nsztUxRCW0BnSoIvykL-n9mWcwi0aQil2N_n5nMjHOHitjtOPNVAtV5IuiqRomjIccON42_1kX-URmIfOZaNwR8EbgpVzZsoStStY6ZJFoaAjrDcNI1TfKhpov36r8A6D5UW7KrFyGNrIV8tdYtGV00BkjCZVLSAL0vL5SR4PBucaMePTvVA3bQu5wYEkgSmw.j3O6RipRm9qIgwoU96EFSCHXXnMJBjUAicPNW96VEQA&amp;dib_tag=se&amp;keywords=3S+8400+mah&amp;qid=1756610025&amp;sr=8-1" xr:uid="{19E65730-6900-417B-BAE6-CAB9289FD747}"/>
     <hyperlink ref="B23" r:id="rId8" xr:uid="{CDAFC55C-E851-401E-BBCF-1C6A02C64874}"/>
     <hyperlink ref="B11" r:id="rId9" xr:uid="{3112BEC5-0070-4734-A13C-033FA815C0C8}"/>
-    <hyperlink ref="B17" r:id="rId10" xr:uid="{E652C524-982E-4015-931D-A51BB57A61B0}"/>
+    <hyperlink ref="B17" r:id="rId10" display="https://www.digikey.ca/short/0zvnp1rd" xr:uid="{E652C524-982E-4015-931D-A51BB57A61B0}"/>
     <hyperlink ref="B7" r:id="rId11" xr:uid="{435C99FE-EDD2-4E84-983E-5B33DA420949}"/>
     <hyperlink ref="B8" r:id="rId12" xr:uid="{9D9F8FA0-0FB8-40F9-964C-907A1BB5FBE6}"/>
   </hyperlinks>
@@ -1086,6 +1092,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="73decd86-39a4-49eb-910d-a9d7478bb842" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000FBE23F23D6C404CAD5DE15B10DA803A" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="173af77996ad3160ba67f97a1dc9a0a1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="73decd86-39a4-49eb-910d-a9d7478bb842" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac7655f4c6b06e1f724061c6ed122ee0" ns3:_="">
     <xsd:import namespace="73decd86-39a4-49eb-910d-a9d7478bb842"/>
@@ -1265,14 +1279,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="73decd86-39a4-49eb-910d-a9d7478bb842" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C9EC6FB-1CF2-4FAD-B830-F4943A84763F}">
   <ds:schemaRefs>
@@ -1282,6 +1288,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BBE388-63B8-4E8B-9309-4F27288A6A4A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="73decd86-39a4-49eb-910d-a9d7478bb842"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E58C759-CD66-46BE-BFED-9AE0DBCB8632}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1297,20 +1319,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BBE388-63B8-4E8B-9309-4F27288A6A4A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="73decd86-39a4-49eb-910d-a9d7478bb842"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>